--- a/data/trans_orig/KIDMED_R3-Edad-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R3-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23188</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18956</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26963</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>61,94%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>50,64%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>72,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>30484</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25058</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>34837</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>65,56%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>53,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>74,93%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26922</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21638</t>
+          <t>23659</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32055</t>
+          <t>32545</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>57405</t>
+          <t>51742</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50289</t>
+          <t>45754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64512</t>
+          <t>57695</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>72,01%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14247</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10472</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18479</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>38,06%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>49,36%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>16011</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11658</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21437</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>34,44%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,07%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>46,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18363</t>
+          <t>14127</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13230</t>
+          <t>10136</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23647</t>
+          <t>19022</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>34374</t>
+          <t>28374</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27267</t>
+          <t>22421</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41490</t>
+          <t>34362</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>42,89%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>108827</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>98736</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>118566</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>69,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>62,87%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>75,5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>112918</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>102588</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>122141</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>70,88%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>64,4%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>76,67%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>125906</t>
+          <t>102538</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>115655</t>
+          <t>92953</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>136095</t>
+          <t>110547</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>238825</t>
+          <t>211364</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>225414</t>
+          <t>198361</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>254027</t>
+          <t>223585</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>48215</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>38476</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>58306</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>30,7%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>24,5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>37,13%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>46381</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37158</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>56711</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>29,12%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>23,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>35,6%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>56053</t>
+          <t>42980</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45864</t>
+          <t>34971</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66304</t>
+          <t>52565</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>102434</t>
+          <t>91196</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87232</t>
+          <t>78975</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>115845</t>
+          <t>104199</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>134851</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>121246</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>145830</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>67,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>60,58%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>72,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>108366</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>95526</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>119783</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>62,61%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>55,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>69,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>142000</t>
+          <t>113870</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>128230</t>
+          <t>102296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155117</t>
+          <t>123860</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>250366</t>
+          <t>248721</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>231676</t>
+          <t>232290</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>266890</t>
+          <t>264429</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>65275</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>54296</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>78880</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,42%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>64706</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53289</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>77546</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>37,39%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30,79%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,81%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70490</t>
+          <t>60802</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57373</t>
+          <t>50812</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84260</t>
+          <t>72376</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>135197</t>
+          <t>126077</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118673</t>
+          <t>110369</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153887</t>
+          <t>142508</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>172157</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>152772</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>189857</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>58,91%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>52,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>64,97%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>197</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>142245</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>96827</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>162781</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>51,86%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>35,3%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>59,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>171288</t>
+          <t>148678</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>145940</t>
+          <t>134224</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>190414</t>
+          <t>162881</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>313534</t>
+          <t>320835</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>262973</t>
+          <t>295345</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>343805</t>
+          <t>345746</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>63,14%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>120064</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>102364</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>139449</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>41,09%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>35,03%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>47,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>132022</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>111486</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>177440</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>48,14%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>40,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>64,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>133711</t>
+          <t>106659</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114585</t>
+          <t>92456</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159059</t>
+          <t>121113</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>265732</t>
+          <t>226723</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>235461</t>
+          <t>201812</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>316293</t>
+          <t>252213</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>46,06%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>439023</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>411473</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>463185</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>59,91%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>585</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>394014</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>342979</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>421661</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>60,33%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>52,51%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>64,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>466116</t>
+          <t>393640</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>435981</t>
+          <t>374528</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>495052</t>
+          <t>412911</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>860130</t>
+          <t>832662</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>796725</t>
+          <t>798965</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>899449</t>
+          <t>863679</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>247801</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>223639</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>275351</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>40,09%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>259120</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>231473</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>310155</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>39,67%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>35,44%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>47,49%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>278617</t>
+          <t>224568</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>249681</t>
+          <t>205297</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>308752</t>
+          <t>243680</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>537737</t>
+          <t>472369</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>498418</t>
+          <t>441352</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>601142</t>
+          <t>506066</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
